--- a/data/trans_orig/IP07A13-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07A13-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2007 (tasa de respuesta: 99,3%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2007 (tasa de respuesta: 99,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8408</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3678</t>
+          <t>3601</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12177</t>
+          <t>11465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>7627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17319</t>
+          <t>17743</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,86%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7635</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15067</t>
+          <t>15320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12093</t>
+          <t>12132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21038</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>22059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33797</t>
+          <t>33890</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,67%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2381</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9128</t>
+          <t>8715</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2643</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9938</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16137</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>3210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13267</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23303</t>
+          <t>23683</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12543</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23298</t>
+          <t>24086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28868</t>
+          <t>28822</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44067</t>
+          <t>44510</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16169</t>
+          <t>15900</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26148</t>
+          <t>26152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25748</t>
+          <t>25341</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37070</t>
+          <t>37788</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>44275</t>
+          <t>45133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61191</t>
+          <t>61388</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,5%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7082</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12522</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16827</t>
+          <t>17274</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>17,02%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3172</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22837</t>
+          <t>22786</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7921</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>16048</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22802</t>
+          <t>23297</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35644</t>
+          <t>36030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>55,07%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10921</t>
+          <t>11600</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21092</t>
+          <t>20567</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19658</t>
+          <t>19692</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25199</t>
+          <t>24871</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>38009</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>3161</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4200</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12703</t>
+          <t>12693</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19172</t>
+          <t>19105</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29015</t>
+          <t>29021</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>18328</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28057</t>
+          <t>28350</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15632</t>
+          <t>16316</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25789</t>
+          <t>25884</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37185</t>
+          <t>37541</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>51218</t>
+          <t>51305</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>48,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>65,92%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,44%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14998</t>
+          <t>14994</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13429</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>26635</t>
+          <t>25836</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>62,83%</t>
+          <t>60,95%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11365</t>
+          <t>11225</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8066</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15741</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>24556</t>
+          <t>25337</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,93%</t>
+          <t>59,77%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>640</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>7156</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15278</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17211</t>
+          <t>16636</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>18118</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>30037</t>
+          <t>29661</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>51,05%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9788</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>18345</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>9479</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17789</t>
+          <t>17616</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>21397</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>33266</t>
+          <t>33811</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>58,19%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>689</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>7603</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>3712</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11948</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>22679</t>
+          <t>23257</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>35262</t>
+          <t>35739</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>18323</t>
+          <t>18836</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>30532</t>
+          <t>30553</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>44883</t>
+          <t>43481</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>62328</t>
+          <t>62229</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>52,57%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>16906</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>29166</t>
+          <t>29101</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>27054</t>
+          <t>27264</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>39315</t>
+          <t>39117</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>46343</t>
+          <t>46279</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>64852</t>
+          <t>64630</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9046</t>
+          <t>8365</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7971</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>14722</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>18792</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>32046</t>
+          <t>31320</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>42,9%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>24628</t>
+          <t>24732</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>38007</t>
+          <t>37487</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>47341</t>
+          <t>46390</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>65564</t>
+          <t>64971</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,74%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>33951</t>
+          <t>35192</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>47625</t>
+          <t>48150</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>31044</t>
+          <t>31853</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>44431</t>
+          <t>44729</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>69300</t>
+          <t>69798</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>88320</t>
+          <t>88953</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,89%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>3781</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>111098</t>
+          <t>112011</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>139940</t>
+          <t>140390</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>115134</t>
+          <t>114200</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>142308</t>
+          <t>142672</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>233703</t>
+          <t>235384</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>273662</t>
+          <t>275696</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>141788</t>
+          <t>143450</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>171510</t>
+          <t>172180</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,0%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>166959</t>
+          <t>167474</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>194767</t>
+          <t>197175</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>317405</t>
+          <t>319018</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>361235</t>
+          <t>359750</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>26588</t>
+          <t>25316</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>44791</t>
+          <t>43078</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>25525</t>
+          <t>25175</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>42267</t>
+          <t>43263</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>56001</t>
+          <t>56956</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>81427</t>
+          <t>80337</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -6532,7 +6532,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>719</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6617,7 +6617,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>4172</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2012 (tasa de respuesta: 96,87%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2012 (tasa de respuesta: 96,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14183</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22170</t>
+          <t>22132</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>21657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33367</t>
+          <t>33946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,74%</t>
+          <t>62,81%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21571</t>
+          <t>21690</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1103</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6935</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11261</t>
+          <t>10973</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15282</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>4648</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7633,7 +7633,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30419</t>
+          <t>30329</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27054</t>
+          <t>28143</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>39336</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50207</t>
+          <t>50552</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66812</t>
+          <t>67334</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13121</t>
+          <t>13262</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23856</t>
+          <t>24231</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10254</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21461</t>
+          <t>20644</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25656</t>
+          <t>25244</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>41916</t>
+          <t>41453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1240</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6900</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10175</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3825</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3357</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4608</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8245,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6586</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6692</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14726</t>
+          <t>14320</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6868</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15830</t>
+          <t>15422</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>15410</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27708</t>
+          <t>27392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,81%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>10761</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18748</t>
+          <t>18480</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>10885</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20727</t>
+          <t>20377</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24063</t>
+          <t>23931</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36256</t>
+          <t>36480</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>63,67%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7800</t>
+          <t>7710</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9091</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6650</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15663</t>
+          <t>15935</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>15186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15106</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28036</t>
+          <t>27684</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>37,94%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21402</t>
+          <t>21228</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30816</t>
+          <t>30652</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14293</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24092</t>
+          <t>23788</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38153</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52144</t>
+          <t>51974</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,23%</t>
         </is>
       </c>
     </row>
@@ -9383,7 +9383,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>3963</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2088</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>3193</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3549</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7510</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9869,12 +9869,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11384</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>6867</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>17244</t>
+          <t>15955</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8739</t>
+          <t>8904</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>16892</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12882</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27712</t>
+          <t>27714</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7848</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6785</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3959</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -10213,7 +10213,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8216</t>
+          <t>9151</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10983</t>
+          <t>11315</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>16615</t>
+          <t>16734</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>25120</t>
+          <t>25225</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12677</t>
+          <t>12411</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>20565</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>32142</t>
+          <t>32328</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>44043</t>
+          <t>44152</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,85%</t>
         </is>
       </c>
     </row>
@@ -10742,12 +10742,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8563</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10757,12 +10757,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2448</t>
+          <t>2658</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>10153</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3535</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>23697</t>
+          <t>24014</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>17284</t>
+          <t>17231</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>29129</t>
+          <t>28775</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>31559</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>48402</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>43,22%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>26465</t>
+          <t>26442</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>38206</t>
+          <t>38776</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>22281</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>34224</t>
+          <t>34128</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>52488</t>
+          <t>52793</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>69330</t>
+          <t>69807</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,33%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2033</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1802</t>
+          <t>1848</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11474,12 +11474,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>13984</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -11537,12 +11537,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>667</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>677</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6609</t>
+          <t>6700</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11622,12 +11622,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>16740</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>29496</t>
+          <t>29295</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>13422</t>
+          <t>14088</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>25737</t>
+          <t>26736</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>32878</t>
+          <t>33806</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>51877</t>
+          <t>51365</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>41260</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>54726</t>
+          <t>54356</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>54,76%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>41673</t>
+          <t>41392</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>55541</t>
+          <t>55241</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>87699</t>
+          <t>87233</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>106973</t>
+          <t>106260</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,54%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>8741</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12286</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7450</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>17951</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>672</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5648</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12294,7 +12294,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>5710</t>
+          <t>5705</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>90558</t>
+          <t>88851</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>117215</t>
+          <t>116629</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>116048</t>
+          <t>115467</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>143773</t>
+          <t>144513</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>214992</t>
+          <t>214694</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>254501</t>
+          <t>253258</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>169633</t>
+          <t>169586</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>198426</t>
+          <t>198595</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>144107</t>
+          <t>145291</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>171993</t>
+          <t>174990</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>321210</t>
+          <t>322979</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>363247</t>
+          <t>364575</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>56,43%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>17758</t>
+          <t>17422</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>33781</t>
+          <t>32626</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>26040</t>
+          <t>25122</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>42677</t>
+          <t>42840</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>46292</t>
+          <t>46228</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>70958</t>
+          <t>70073</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>6514</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>3292</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>14228</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -13019,7 +13019,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5403</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4702</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>695</t>
+          <t>817</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse comprendido por sus padres en 2016 (tasa de respuesta: 98,43%)</t>
+          <t>Menores según la frecuencia de sentirse comprendido por sus padres, percibida por el adulto en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13701</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13500,7 +13500,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3898</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>10903</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11401</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23176</t>
+          <t>22514</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10146</t>
+          <t>10394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19138</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>13722</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21553</t>
+          <t>21700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26130</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38569</t>
+          <t>37796</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>66,74%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2534</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8818</t>
+          <t>9047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5457</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3971</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3400</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13839,7 +13839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31476</t>
+          <t>30689</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41860</t>
+          <t>41863</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,7 +14177,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35374</t>
+          <t>35240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47177</t>
+          <t>46999</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69524</t>
+          <t>69589</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85070</t>
+          <t>85706</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>62,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11057</t>
+          <t>11054</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21441</t>
+          <t>22228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10249</t>
+          <t>10360</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>22076</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24757</t>
+          <t>24489</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39953</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,49%</t>
         </is>
       </c>
     </row>
@@ -14428,7 +14428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3373</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14463,7 +14463,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17098</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>27681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17930</t>
+          <t>17607</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27147</t>
+          <t>27101</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>52,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37782</t>
+          <t>37869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51725</t>
+          <t>51485</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,01%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>7484</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18106</t>
+          <t>18056</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5069</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13349</t>
+          <t>13644</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14890</t>
+          <t>15441</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28398</t>
+          <t>28190</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4366</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>712</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>753</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19585</t>
+          <t>18970</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>29066</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25542</t>
+          <t>25454</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35738</t>
+          <t>36129</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48409</t>
+          <t>48346</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62337</t>
+          <t>62907</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>75,58%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16329</t>
+          <t>16713</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>2997</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11796</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12986</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25146</t>
+          <t>25235</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,32%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1760</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>7915</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,12 +15767,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>1698</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8952</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4806</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>13363</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -15905,7 +15905,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4136</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15940,7 +15940,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3553</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>17100</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>14717</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>25810</t>
+          <t>25163</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>55,47%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>9263</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16095</t>
+          <t>16214</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>17038</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>19557</t>
+          <t>20204</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>30650</t>
+          <t>30910</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>68,13%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18325</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>26550</t>
+          <t>27072</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>20890</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>28197</t>
+          <t>28186</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>42327</t>
+          <t>42318</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>53094</t>
+          <t>52917</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,18%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7980</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>5818</t>
+          <t>5875</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>15202</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>726</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17347,7 +17347,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17362,7 +17362,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17417,7 +17417,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17432,7 +17432,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>17739</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>30279</t>
+          <t>29625</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>12258</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>24250</t>
+          <t>25111</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>33016</t>
+          <t>32260</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>51079</t>
+          <t>50170</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>30227</t>
+          <t>30602</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>44252</t>
+          <t>44184</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>31671</t>
+          <t>32551</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>45019</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>67140</t>
+          <t>66678</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>86053</t>
+          <t>85704</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,15%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>9217</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3422</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>12059</t>
+          <t>11568</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6657</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5213</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18044,7 +18044,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18114,7 +18114,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>33907</t>
+          <t>34014</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>27817</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>42749</t>
+          <t>41756</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>53263</t>
+          <t>52652</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>72588</t>
+          <t>72622</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>36701</t>
+          <t>37130</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>50436</t>
+          <t>51150</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>26209</t>
+          <t>26792</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>40160</t>
+          <t>40782</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>66853</t>
+          <t>66753</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>87100</t>
+          <t>87168</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,99%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3823</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3268</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>8260</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>19627</t>
+          <t>19475</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3980</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18648,7 +18648,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18663,12 +18663,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>527</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>5376</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -18746,57 +18746,57 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
+          <t>2990</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>3,94%</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
           <t>2998</t>
         </is>
       </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R50" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>3596</t>
-        </is>
-      </c>
-      <c r="U50" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>157027</t>
+          <t>157612</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>190398</t>
+          <t>187861</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>176908</t>
+          <t>179298</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>208856</t>
+          <t>209545</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>344438</t>
+          <t>342511</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>390059</t>
+          <t>390229</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>138211</t>
+          <t>140888</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>171255</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>123261</t>
+          <t>123327</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>154751</t>
+          <t>153934</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>270164</t>
+          <t>272051</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>313949</t>
+          <t>315585</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,18%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>15787</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>32062</t>
+          <t>30961</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>16921</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>36743</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>58177</t>
+          <t>59550</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,34%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>7424</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5167</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>2064</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9256</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2969</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>588</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>6369</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
